--- a/Data/Building/Lab.AirQuality.xlsx
+++ b/Data/Building/Lab.AirQuality.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252822</v>
+        <v>1711844516</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709253916</v>
+        <v>1711845579</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +562,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709261803</v>
+        <v>1711853394</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +576,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709268235</v>
+        <v>1711859282</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +609,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709273747</v>
+        <v>1711867532</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +642,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709246316</v>
+        <v>1711925098</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +675,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709247072</v>
+        <v>1711926068</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709264933</v>
+        <v>1711938802</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +741,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709265632</v>
+        <v>1711943421</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +774,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +793,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709333079</v>
+        <v>1712011346</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +807,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +826,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709334091</v>
+        <v>1712012471</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +840,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +859,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709345665</v>
+        <v>1712024269</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +873,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +892,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709352149</v>
+        <v>1712033695</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +906,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +925,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709418805</v>
+        <v>1712098352</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +939,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +958,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709418857</v>
+        <v>1712099248</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +972,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +991,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709419860</v>
+        <v>1712113294</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1001,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1024,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709439783</v>
+        <v>1712121140</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1034,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1057,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709440165</v>
+        <v>1712182070</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1071,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1090,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709440931</v>
+        <v>1712182097</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1100,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1123,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709505119</v>
+        <v>1712182865</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1133,15 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Good</t>
+          <t>Lab.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1160,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709505203</v>
+        <v>1712204169</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1174,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1193,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709506263</v>
+        <v>1712204553</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1203,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1226,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709513462</v>
+        <v>1712205271</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1236,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1259,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709514318</v>
+        <v>1712269161</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1269,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1292,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709517024</v>
+        <v>1712269941</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1306,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1325,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709523418</v>
+        <v>1712280903</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1358,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709526184</v>
+        <v>1712290948</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1372,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1391,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709592658</v>
+        <v>1712530887</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1405,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1424,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709592686</v>
+        <v>1712531943</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1438,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1457,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709593500</v>
+        <v>1712553086</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1467,11 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1490,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709604919</v>
+        <v>1712553757</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1500,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1523,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709611920</v>
+        <v>1712617557</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1537,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1556,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709614798</v>
+        <v>1712618551</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1566,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1589,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709775479</v>
+        <v>1712630333</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1603,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1622,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709850044</v>
+        <v>1712637024</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1632,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1655,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709850882</v>
+        <v>1712704733</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1665,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1688,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709868172</v>
+        <v>1712705839</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1702,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1721,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709868535</v>
+        <v>1712722812</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1735,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1754,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709869278</v>
+        <v>1712723553</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1768,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1787,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709937677</v>
+        <v>1712791244</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1801,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1820,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709938517</v>
+        <v>1712791297</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1834,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1853,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709949280</v>
+        <v>1712792240</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1863,15 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Good</t>
+          <t>Lab.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1890,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709957765</v>
+        <v>1712801804</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1900,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1923,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710025211</v>
+        <v>1712807456</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1937,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1956,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710026253</v>
+        <v>1712810486</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1966,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1989,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710026254</v>
+        <v>1712813314</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +1999,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2022,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710033201</v>
+        <v>1712875746</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2036,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2055,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710039143</v>
+        <v>1712876820</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2065,15 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Good</t>
+          <t>Lab.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2092,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710047034</v>
+        <v>1712894020</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2102,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2125,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710111372</v>
+        <v>1712894417</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2139,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2158,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710112318</v>
+        <v>1712895133</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2168,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2191,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710123417</v>
+        <v>1713134469</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2205,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2224,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710134854</v>
+        <v>1713135420</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2234,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2257,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710197215</v>
+        <v>1713148520</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2271,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2290,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710198309</v>
+        <v>1713155165</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2300,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2323,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710198309</v>
+        <v>1713220065</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2333,11 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2356,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710207703</v>
+        <v>1713220838</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2370,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2389,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710213755</v>
+        <v>1713235815</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2403,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2422,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710218798</v>
+        <v>1713239669</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2436,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2455,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710456416</v>
+        <v>1713307479</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2469,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2488,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710457408</v>
+        <v>1713308382</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2502,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2521,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710470220</v>
+        <v>1713320994</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2535,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2554,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710476444</v>
+        <v>1713325176</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2568,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2587,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710542268</v>
+        <v>1713327355</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2601,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2620,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710543225</v>
+        <v>1713392559</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2634,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2653,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710543227</v>
+        <v>1713393424</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2667,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2690,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710563017</v>
+        <v>1713402048</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2704,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2723,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710563391</v>
+        <v>1713407877</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2737,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2756,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710564184</v>
+        <v>1713410559</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2770,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2789,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710630444</v>
+        <v>1713413470</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2803,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2822,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710631403</v>
+        <v>1713480735</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2836,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2855,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710643579</v>
+        <v>1713480884</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2865,15 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Good</t>
+          <t>Lab.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2892,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710654476</v>
+        <v>1713488686</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2902,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2925,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710716066</v>
+        <v>1713494415</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2939,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2958,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710717068</v>
+        <v>1713499996</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +2968,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2991,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710728301</v>
+        <v>1713738406</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3005,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3024,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710736701</v>
+        <v>1713739336</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2929,10 +3034,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3057,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710802203</v>
+        <v>1713750090</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3071,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3090,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710803278</v>
+        <v>1713755859</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3100,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3123,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710817514</v>
+        <v>1713758789</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3137,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3156,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710823811</v>
+        <v>1713825571</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3166,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3189,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1711060273</v>
+        <v>1713826435</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3199,15 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Good</t>
+          <t>Lab.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3226,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1711061328</v>
+        <v>1713836324</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3240,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3259,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1711061328</v>
+        <v>1713842525</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3269,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: SeverePollution</t>
+          <t>Lab.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3292,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1711072834</v>
+        <v>1713847642</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3302,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Poor</t>
+          <t>Lab.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3325,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1711079322</v>
+        <v>1713911576</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3339,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3358,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1711081981</v>
+        <v>1713912456</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3368,11 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Excellent</t>
+          <t>Lab.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3391,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1711147340</v>
+        <v>1713912458</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3401,15 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lab.AirQuality.state: Good</t>
+          <t>Lab.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3428,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1711148404</v>
+        <v>1713929902</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3442,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3461,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1711170430</v>
+        <v>1713930285</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3475,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3494,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1711171209</v>
+        <v>1713931027</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3508,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3527,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1711233525</v>
+        <v>1713933177</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3541,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3560,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1711233631</v>
+        <v>1713933251</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3574,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3593,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1711234390</v>
+        <v>1713997315</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3607,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3630,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1711253110</v>
+        <v>1714011567</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3644,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3663,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1711253509</v>
+        <v>1714014440</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3677,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3696,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1711254306</v>
+        <v>1714015199</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3710,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3729,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1711319917</v>
+        <v>1714084106</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3743,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3762,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1711320859</v>
+        <v>1714084892</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3776,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3795,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711320859</v>
+        <v>1714090311</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3809,11 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3832,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1711329035</v>
+        <v>1714099981</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3846,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3865,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1711335378</v>
+        <v>1714100671</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3879,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3898,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711337946</v>
+        <v>1714101418</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3912,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3931,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711406901</v>
+        <v>1714284024</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,102 +3945,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>AirQuality_Change</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1711407865</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Lab.AirQuality.state: Poor</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>AirQuality_Change</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>1711424358</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Lab.AirQuality.state: Good</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>AirQuality_Change</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1711428452</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Lab.AirQuality.state: Excellent</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
